--- a/Results/onnv_chik_model_posterior_estimates.xlsx
+++ b/Results/onnv_chik_model_posterior_estimates.xlsx
@@ -398,13 +398,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.9944975</v>
+        <v>0.9935229999999999</v>
       </c>
       <c r="D2">
-        <v>0.9684657999999999</v>
+        <v>0.9676549250000001</v>
       </c>
       <c r="E2">
-        <v>1.020931</v>
+        <v>1.0199615</v>
       </c>
     </row>
     <row r="3">
@@ -419,13 +419,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.9657895000000001</v>
+        <v>0.9609685</v>
       </c>
       <c r="D3">
-        <v>0.929519325</v>
+        <v>0.9244993500000001</v>
       </c>
       <c r="E3">
-        <v>1.00378075</v>
+        <v>0.9978511249999999</v>
       </c>
     </row>
     <row r="4">
@@ -440,13 +440,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.47146</v>
+        <v>0.5035240000000001</v>
       </c>
       <c r="D4">
-        <v>0.34152785</v>
+        <v>0.3684877</v>
       </c>
       <c r="E4">
-        <v>0.5893825249999999</v>
+        <v>0.6292295999999999</v>
       </c>
     </row>
     <row r="5">
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.231459</v>
+        <v>0.248977</v>
       </c>
       <c r="D5">
-        <v>0.14570715</v>
+        <v>0.1523003</v>
       </c>
       <c r="E5">
-        <v>0.347147975</v>
+        <v>0.3758950249999999</v>
       </c>
     </row>
   </sheetData>
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>6.57378</v>
+        <v>6.57301</v>
       </c>
       <c r="D2">
-        <v>6.543199749999999</v>
+        <v>6.54208975</v>
       </c>
       <c r="E2">
-        <v>6.602560750000001</v>
+        <v>6.6011905</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ONNV</t>
+          <t>ONNV Antigen</t>
         </is>
       </c>
     </row>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>3.9049263825</v>
+        <v>4.172431485040001</v>
       </c>
       <c r="D3">
-        <v>2.768695754448975</v>
+        <v>2.98461310833175</v>
       </c>
       <c r="E3">
-        <v>4.981744594294525</v>
+        <v>5.323599390410999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ONNV</t>
+          <t>ONNV Antigen</t>
         </is>
       </c>
     </row>
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>8.282624999999999</v>
+        <v>8.28646</v>
       </c>
       <c r="D4">
-        <v>8.1067935</v>
+        <v>8.099627499999999</v>
       </c>
       <c r="E4">
-        <v>8.452481000000001</v>
+        <v>8.460503749999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CHIK</t>
+          <t>CHIK Antigen</t>
         </is>
       </c>
     </row>
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>6.537607775550001</v>
+        <v>6.530436614229999</v>
       </c>
       <c r="D5">
-        <v>6.336865180443549</v>
+        <v>6.330485366379519</v>
       </c>
       <c r="E5">
-        <v>6.74075894905825</v>
+        <v>6.73296016416575</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CHIK</t>
+          <t>CHIK Antigen</t>
         </is>
       </c>
     </row>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>4.53796</v>
+        <v>4.5408</v>
       </c>
       <c r="D2">
-        <v>4.507296999999999</v>
+        <v>4.50989</v>
       </c>
       <c r="E2">
-        <v>4.56910025</v>
+        <v>4.5704905</v>
       </c>
     </row>
     <row r="3">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>6.109605</v>
+        <v>6.11324</v>
       </c>
       <c r="D3">
-        <v>6.079799</v>
+        <v>6.08286</v>
       </c>
       <c r="E3">
-        <v>6.13823175</v>
+        <v>6.1439305</v>
       </c>
     </row>
     <row r="4">
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>5.346215</v>
+        <v>5.35785</v>
       </c>
       <c r="D4">
-        <v>5.307688000000001</v>
+        <v>5.31780975</v>
       </c>
       <c r="E4">
-        <v>5.3852705</v>
+        <v>5.3975915</v>
       </c>
     </row>
     <row r="5">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>8.13424</v>
+        <v>8.13209</v>
       </c>
       <c r="D5">
-        <v>8.077558249999999</v>
+        <v>8.0747985</v>
       </c>
       <c r="E5">
-        <v>8.191800750000001</v>
+        <v>8.19019275</v>
       </c>
     </row>
     <row r="6">
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>7.31174</v>
+        <v>7.310525</v>
       </c>
       <c r="D6">
-        <v>7.23753775</v>
+        <v>7.23414825</v>
       </c>
       <c r="E6">
-        <v>7.391320250000001</v>
+        <v>7.388651</v>
       </c>
     </row>
     <row r="7">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>5.55708</v>
+        <v>5.62936</v>
       </c>
       <c r="D7">
-        <v>5.280703</v>
+        <v>5.3424695</v>
       </c>
       <c r="E7">
-        <v>5.836719749999999</v>
+        <v>5.93205175</v>
       </c>
     </row>
     <row r="8">
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="C8">
-        <v>5.848174999999999</v>
+        <v>5.89587</v>
       </c>
       <c r="D8">
-        <v>5.653248</v>
+        <v>5.6769645</v>
       </c>
       <c r="E8">
-        <v>6.12244375</v>
+        <v>6.19311175</v>
       </c>
     </row>
     <row r="9">
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="C9">
-        <v>7.81674</v>
+        <v>7.850474999999999</v>
       </c>
       <c r="D9">
-        <v>7.6092995</v>
+        <v>7.621139749999999</v>
       </c>
       <c r="E9">
-        <v>8.099777249999999</v>
+        <v>8.15827125</v>
       </c>
     </row>
   </sheetData>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>6.57378</v>
+        <v>6.57301</v>
       </c>
       <c r="D2">
-        <v>6.543199749999999</v>
+        <v>6.54208975</v>
       </c>
       <c r="E2">
-        <v>6.602560750000001</v>
+        <v>6.6011905</v>
       </c>
     </row>
     <row r="3">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>8.282624999999999</v>
+        <v>8.28646</v>
       </c>
       <c r="D3">
-        <v>8.1067935</v>
+        <v>8.099627499999999</v>
       </c>
       <c r="E3">
-        <v>8.452481000000001</v>
+        <v>8.460503749999999</v>
       </c>
     </row>
     <row r="4">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>6.57378</v>
+        <v>6.57301</v>
       </c>
       <c r="D4">
-        <v>6.543199749999999</v>
+        <v>6.54208975</v>
       </c>
       <c r="E4">
-        <v>6.602560750000001</v>
+        <v>6.6011905</v>
       </c>
     </row>
     <row r="5">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>8.282624999999999</v>
+        <v>8.28646</v>
       </c>
       <c r="D5">
-        <v>8.1067935</v>
+        <v>8.099627499999999</v>
       </c>
       <c r="E5">
-        <v>8.452481000000001</v>
+        <v>8.460503749999999</v>
       </c>
     </row>
   </sheetData>
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.2317765</v>
+        <v>0.235212</v>
       </c>
       <c r="C2">
-        <v>0.21676185</v>
+        <v>0.219818275</v>
       </c>
       <c r="D2">
-        <v>0.247484375</v>
+        <v>0.251141075</v>
       </c>
     </row>
     <row r="3">
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.01737335</v>
+        <v>0.0171676</v>
       </c>
       <c r="C3">
-        <v>0.01058751</v>
+        <v>0.01021325</v>
       </c>
       <c r="D3">
-        <v>0.02580483749999999</v>
+        <v>0.02630976</v>
       </c>
     </row>
   </sheetData>
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.7693384999999999</v>
+        <v>0.7668735</v>
       </c>
       <c r="D2">
-        <v>0.748721725</v>
+        <v>0.7460338999999999</v>
       </c>
       <c r="E2">
-        <v>0.7908675249999999</v>
+        <v>0.788755075</v>
       </c>
     </row>
     <row r="3">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.7521485</v>
+        <v>0.750057</v>
       </c>
       <c r="D3">
-        <v>0.735283525</v>
+        <v>0.732158675</v>
       </c>
       <c r="E3">
-        <v>0.769891</v>
+        <v>0.7676470249999999</v>
       </c>
     </row>
     <row r="4">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>1.179335</v>
+        <v>1.1727</v>
       </c>
       <c r="D4">
-        <v>1.15633925</v>
+        <v>1.150209</v>
       </c>
       <c r="E4">
-        <v>1.20272</v>
+        <v>1.1963005</v>
       </c>
     </row>
     <row r="5">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.367953</v>
+        <v>0.368534</v>
       </c>
       <c r="D5">
-        <v>0.34413295</v>
+        <v>0.343957475</v>
       </c>
       <c r="E5">
-        <v>0.3939147</v>
+        <v>0.3951855</v>
       </c>
     </row>
   </sheetData>
